--- a/output/DTR_7-4_GALLEGOS.xlsx
+++ b/output/DTR_7-4_GALLEGOS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
   <si>
     <t>Republic of the Philippines</t>
   </si>
@@ -74,6 +74,18 @@
   </si>
   <si>
     <t>Minutes</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Eid'l Fitr</t>
+  </si>
+  <si>
+    <t>Sunday / Palm Sunday</t>
   </si>
   <si>
     <t>Total</t>
@@ -858,7 +870,9 @@
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="H19" s="23"/>
+      <c r="H19" s="23" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="20" spans="1:11" s="7" customFormat="1">
       <c r="A20" s="22">
@@ -918,7 +932,9 @@
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="H25" s="23"/>
+      <c r="H25" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="26" spans="1:11" s="7" customFormat="1">
       <c r="A26" s="21">
@@ -928,14 +944,16 @@
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="H26" s="23"/>
+      <c r="H26" s="23" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="27" spans="1:11" s="7" customFormat="1">
       <c r="A27" s="22">
         <v>9</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -947,7 +965,7 @@
         <v>10</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -959,7 +977,7 @@
         <v>11</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -971,7 +989,7 @@
         <v>12</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -983,7 +1001,7 @@
         <v>13</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -998,7 +1016,9 @@
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
-      <c r="H32" s="23"/>
+      <c r="H32" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="33" spans="1:11" s="7" customFormat="1">
       <c r="A33" s="21">
@@ -1008,14 +1028,16 @@
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
-      <c r="H33" s="23"/>
+      <c r="H33" s="23" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="34" spans="1:11" s="7" customFormat="1">
       <c r="A34" s="22">
         <v>16</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -1027,7 +1049,7 @@
         <v>17</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -1039,7 +1061,7 @@
         <v>18</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -1064,7 +1086,9 @@
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="H38" s="23"/>
+      <c r="H38" s="23" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="39" spans="1:11" s="8" customFormat="1">
       <c r="A39" s="21">
@@ -1074,7 +1098,9 @@
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
-      <c r="H39" s="23"/>
+      <c r="H39" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="40" spans="1:11" s="7" customFormat="1">
       <c r="A40" s="21">
@@ -1084,14 +1110,16 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
-      <c r="H40" s="23"/>
+      <c r="H40" s="23" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="41" spans="1:11" s="7" customFormat="1">
       <c r="A41" s="22">
         <v>23</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -1103,7 +1131,7 @@
         <v>24</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
@@ -1115,7 +1143,7 @@
         <v>25</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -1137,7 +1165,7 @@
         <v>27</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -1152,7 +1180,9 @@
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="H46" s="23"/>
+      <c r="H46" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="47" spans="1:11" s="7" customFormat="1">
       <c r="A47" s="21">
@@ -1162,14 +1192,16 @@
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
-      <c r="H47" s="23"/>
+      <c r="H47" s="23" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="48" spans="1:11" s="7" customFormat="1">
       <c r="A48" s="24">
         <v>30</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
@@ -1181,7 +1213,7 @@
         <v>31</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
@@ -1190,7 +1222,7 @@
     </row>
     <row r="50" spans="1:11" s="7" customFormat="1">
       <c r="A50" s="25" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G50" s="26" t="str">
         <f>SUM(G20:G49)</f>
@@ -1201,12 +1233,12 @@
     <row r="51" spans="1:11" s="7" customFormat="1"/>
     <row r="52" spans="1:11" s="7" customFormat="1">
       <c r="A52" s="27" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="7" customFormat="1">
       <c r="A53" s="7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:11" customHeight="1" ht="15" s="7" customFormat="1"/>
@@ -1217,29 +1249,29 @@
     </row>
     <row r="56" spans="1:11" s="7" customFormat="1">
       <c r="A56" s="29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:11" s="7" customFormat="1"/>
     <row r="58" spans="1:11" s="7" customFormat="1">
       <c r="A58" s="30" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="7" customFormat="1">
       <c r="B59" s="31" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:11" s="7" customFormat="1"/>
     <row r="61" spans="1:11" s="7" customFormat="1">
       <c r="A61" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="7" customFormat="1">
       <c r="A62" s="16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:11" customHeight="1" ht="15" s="7" customFormat="1"/>
@@ -1330,47 +1362,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/output/DTR_7-4_GALLEGOS.xlsx
+++ b/output/DTR_7-4_GALLEGOS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
   <si>
     <t>Republic of the Philippines</t>
   </si>
@@ -112,31 +112,67 @@
     <t>Assistant Schools Division Superintedent</t>
   </si>
   <si>
+    <t>15:36</t>
+  </si>
+  <si>
     <t>06:56</t>
   </si>
   <si>
+    <t>15:32</t>
+  </si>
+  <si>
     <t>06:59</t>
   </si>
   <si>
     <t>07:02</t>
   </si>
   <si>
+    <t>15:28</t>
+  </si>
+  <si>
     <t>07:05</t>
   </si>
   <si>
+    <t>15:27</t>
+  </si>
+  <si>
     <t>06:51</t>
   </si>
   <si>
+    <t>15:26</t>
+  </si>
+  <si>
     <t>06:55</t>
   </si>
   <si>
+    <t>15:43</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>15:21</t>
+  </si>
+  <si>
     <t>06:58</t>
   </si>
   <si>
+    <t>15:23</t>
+  </si>
+  <si>
+    <t>15:22</t>
+  </si>
+  <si>
     <t>07:14</t>
   </si>
   <si>
+    <t>15:57</t>
+  </si>
+  <si>
     <t>07:21</t>
+  </si>
+  <si>
+    <t>16:10</t>
   </si>
   <si>
     <t>07:04</t>
@@ -921,7 +957,9 @@
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
+      <c r="E24" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="H24" s="7"/>
     </row>
     <row r="25" spans="1:11" s="7" customFormat="1">
@@ -953,11 +991,13 @@
         <v>9</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
+      <c r="E27" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="H27" s="7"/>
     </row>
     <row r="28" spans="1:11" s="7" customFormat="1">
@@ -965,11 +1005,13 @@
         <v>10</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
+      <c r="E28" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="H28" s="7"/>
     </row>
     <row r="29" spans="1:11" s="7" customFormat="1">
@@ -977,11 +1019,13 @@
         <v>11</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
+      <c r="E29" s="7" t="s">
+        <v>35</v>
+      </c>
       <c r="H29" s="7"/>
     </row>
     <row r="30" spans="1:11" s="7" customFormat="1">
@@ -989,11 +1033,13 @@
         <v>12</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
+      <c r="E30" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="H30" s="7"/>
     </row>
     <row r="31" spans="1:11" s="7" customFormat="1">
@@ -1001,11 +1047,13 @@
         <v>13</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
+      <c r="E31" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="H31" s="7"/>
     </row>
     <row r="32" spans="1:11" s="7" customFormat="1">
@@ -1037,11 +1085,13 @@
         <v>16</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
+      <c r="E34" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="H34" s="7"/>
     </row>
     <row r="35" spans="1:11" s="7" customFormat="1">
@@ -1049,11 +1099,13 @@
         <v>17</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+      <c r="E35" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="H35" s="7"/>
     </row>
     <row r="36" spans="1:11" s="7" customFormat="1">
@@ -1061,11 +1113,13 @@
         <v>18</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
+      <c r="E36" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="H36" s="7"/>
     </row>
     <row r="37" spans="1:11" s="7" customFormat="1">
@@ -1119,11 +1173,13 @@
         <v>23</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
+      <c r="E41" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="H41" s="7"/>
     </row>
     <row r="42" spans="1:11" s="8" customFormat="1">
@@ -1131,11 +1187,13 @@
         <v>24</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
+      <c r="E42" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="H42" s="8"/>
     </row>
     <row r="43" spans="1:11" s="8" customFormat="1">
@@ -1143,11 +1201,13 @@
         <v>25</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
+      <c r="E43" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="H43" s="8"/>
     </row>
     <row r="44" spans="1:11" s="8" customFormat="1">
@@ -1165,11 +1225,13 @@
         <v>27</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
+      <c r="E45" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="H45" s="7"/>
     </row>
     <row r="46" spans="1:11" s="7" customFormat="1">
@@ -1201,11 +1263,13 @@
         <v>30</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
+      <c r="E48" s="7" t="s">
+        <v>50</v>
+      </c>
       <c r="H48" s="7"/>
     </row>
     <row r="49" spans="1:11" s="7" customFormat="1">
@@ -1213,11 +1277,13 @@
         <v>31</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
+      <c r="E49" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="H49" s="7"/>
     </row>
     <row r="50" spans="1:11" s="7" customFormat="1">
@@ -1362,47 +1428,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
